--- a/data/actions/action_database_other_cbas.xlsx
+++ b/data/actions/action_database_other_cbas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/cc_offshore_wind/osw_mitigation_measures/data/actions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C42715-FAE6-DB48-BD0D-0C984864CA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC9D0F7-9598-4F47-8AC7-88C62C5BC615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="500" windowWidth="33280" windowHeight="21900" activeTab="1" xr2:uid="{D2A3E31B-314F-BE48-832E-3F962C44E348}"/>
+    <workbookView xWindow="660" yWindow="500" windowWidth="33280" windowHeight="21900" xr2:uid="{D2A3E31B-314F-BE48-832E-3F962C44E348}"/>
   </bookViews>
   <sheets>
     <sheet name="Actions" sheetId="1" r:id="rId1"/>
@@ -559,9 +559,6 @@
     <t>Support tribal capacity to engage with the OSW project</t>
   </si>
   <si>
-    <t>Fund public school supplies and programming (training aids, equipment, indigenous history curricula)</t>
-  </si>
-  <si>
     <t>Support tribal capacity for co-management of natural resources</t>
   </si>
   <si>
@@ -725,6 +722,9 @@
   </si>
   <si>
     <t>Fund a third-party to evaluate the fishery impacts of the OSW project</t>
+  </si>
+  <si>
+    <t>Fund public school supplies and programming</t>
   </si>
 </sst>
 </file>
@@ -1239,7 +1239,7 @@
         <v>80</v>
       </c>
       <c r="F3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G3" t="s">
         <v>151</v>
@@ -1265,7 +1265,7 @@
         <v>81</v>
       </c>
       <c r="F4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G4" t="s">
         <v>151</v>
@@ -1288,10 +1288,10 @@
         <v>82</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G5" t="s">
-        <v>171</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -1334,7 +1334,7 @@
         <v>49</v>
       </c>
       <c r="F7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G7" t="s">
         <v>151</v>
@@ -1415,22 +1415,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B11" t="s">
         <v>199</v>
       </c>
-      <c r="B11" t="s">
-        <v>200</v>
-      </c>
       <c r="C11" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D11" s="6">
         <v>1</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G11" t="s">
         <v>153</v>
@@ -1438,19 +1438,19 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" t="s">
         <v>199</v>
       </c>
-      <c r="B12" t="s">
-        <v>200</v>
-      </c>
       <c r="C12" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D12" s="6">
         <v>2</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>159</v>
@@ -1461,22 +1461,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13" t="s">
         <v>199</v>
       </c>
-      <c r="B13" t="s">
-        <v>200</v>
-      </c>
       <c r="C13" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D13" s="6">
         <v>3</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G13" t="s">
         <v>164</v>
@@ -1484,22 +1484,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14" t="s">
         <v>199</v>
       </c>
-      <c r="B14" t="s">
-        <v>200</v>
-      </c>
       <c r="C14" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D14" s="6">
         <v>4</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G14" t="s">
         <v>153</v>
@@ -1546,7 +1546,7 @@
         <v>36</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G16" t="s">
         <v>164</v>
@@ -1748,7 +1748,7 @@
         <v>53</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G24" t="s">
         <v>152</v>
@@ -1878,7 +1878,7 @@
         <v>56</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G29" t="s">
         <v>164</v>
@@ -1956,7 +1956,7 @@
         <v>62</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G32" t="s">
         <v>152</v>
@@ -2006,7 +2006,7 @@
         <v>44</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G34" t="s">
         <v>151</v>
@@ -2030,10 +2030,10 @@
         <v>47</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H35" s="4"/>
     </row>
@@ -2102,7 +2102,7 @@
         <v>9</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G38" t="s">
         <v>151</v>
@@ -2128,7 +2128,7 @@
         <v>12</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G39" t="s">
         <v>164</v>
@@ -2152,7 +2152,7 @@
         <v>40</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G40" t="s">
         <v>151</v>
@@ -2200,7 +2200,7 @@
         <v>38</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G42" t="s">
         <v>152</v>
@@ -2257,22 +2257,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B45" t="s">
         <v>206</v>
       </c>
-      <c r="B45" t="s">
-        <v>207</v>
-      </c>
       <c r="C45" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D45" s="6">
         <v>5</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G45" t="s">
         <v>151</v>
@@ -2280,22 +2280,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B46" t="s">
         <v>206</v>
       </c>
-      <c r="B46" t="s">
-        <v>207</v>
-      </c>
       <c r="C46" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D46" s="6">
         <v>6</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G46" t="s">
         <v>151</v>
@@ -2303,22 +2303,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B47" t="s">
         <v>206</v>
       </c>
-      <c r="B47" t="s">
-        <v>207</v>
-      </c>
       <c r="C47" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D47" s="6">
         <v>7</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G47" t="s">
         <v>152</v>
@@ -2326,22 +2326,22 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B48" t="s">
         <v>206</v>
       </c>
-      <c r="B48" t="s">
-        <v>207</v>
-      </c>
       <c r="C48" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D48" s="6">
         <v>8</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F48" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G48" t="s">
         <v>165</v>
@@ -2349,22 +2349,22 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B49" t="s">
         <v>206</v>
       </c>
-      <c r="B49" t="s">
-        <v>207</v>
-      </c>
       <c r="C49" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D49" s="6">
         <v>9</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F49" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G49" t="s">
         <v>165</v>
@@ -2372,22 +2372,22 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B50" t="s">
         <v>206</v>
       </c>
-      <c r="B50" t="s">
-        <v>207</v>
-      </c>
       <c r="C50" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D50" s="6">
         <v>10</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G50" t="s">
         <v>151</v>
@@ -2395,22 +2395,22 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B51" t="s">
         <v>206</v>
       </c>
-      <c r="B51" t="s">
-        <v>207</v>
-      </c>
       <c r="C51" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D51" s="6">
         <v>11</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G51" t="s">
         <v>164</v>
@@ -2418,48 +2418,48 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B52" t="s">
         <v>206</v>
       </c>
-      <c r="B52" t="s">
-        <v>207</v>
-      </c>
       <c r="C52" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D52" s="6">
         <v>12</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F52" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G52" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B53" t="s">
         <v>206</v>
       </c>
-      <c r="B53" t="s">
-        <v>207</v>
-      </c>
       <c r="C53" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D53" s="6">
         <v>13</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -2527,7 +2527,7 @@
         <v>43</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G56" t="s">
         <v>151</v>
@@ -2597,7 +2597,7 @@
         <v>129</v>
       </c>
       <c r="F59" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G59" t="s">
         <v>165</v>
@@ -2620,7 +2620,7 @@
         <v>101</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G60" t="s">
         <v>153</v>
@@ -2643,7 +2643,7 @@
         <v>102</v>
       </c>
       <c r="F61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G61" t="s">
         <v>148</v>
@@ -2666,7 +2666,7 @@
         <v>103</v>
       </c>
       <c r="F62" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G62" t="s">
         <v>148</v>
@@ -2689,7 +2689,7 @@
         <v>104</v>
       </c>
       <c r="F63" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G63" t="s">
         <v>148</v>
@@ -2712,7 +2712,7 @@
         <v>105</v>
       </c>
       <c r="F64" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G64" t="s">
         <v>148</v>
@@ -2738,7 +2738,7 @@
         <v>156</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -2758,7 +2758,7 @@
         <v>131</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G66" t="s">
         <v>152</v>
@@ -2781,10 +2781,10 @@
         <v>132</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G67" t="s">
-        <v>171</v>
+        <v>226</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -2873,7 +2873,7 @@
         <v>113</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G71" t="s">
         <v>151</v>
@@ -2896,7 +2896,7 @@
         <v>135</v>
       </c>
       <c r="F72" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G72" t="s">
         <v>165</v>
@@ -2919,7 +2919,7 @@
         <v>136</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G73" t="s">
         <v>164</v>
@@ -2942,10 +2942,10 @@
         <v>115</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G74" t="s">
-        <v>171</v>
+        <v>226</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
@@ -2965,7 +2965,7 @@
         <v>137</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G75" t="s">
         <v>164</v>
@@ -3057,10 +3057,10 @@
         <v>147</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G79" t="s">
-        <v>171</v>
+        <v>226</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
@@ -3080,7 +3080,7 @@
         <v>138</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G80" t="s">
         <v>164</v>
@@ -3126,7 +3126,7 @@
         <v>122</v>
       </c>
       <c r="F82" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G82" t="s">
         <v>151</v>
@@ -3149,7 +3149,7 @@
         <v>140</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G83" t="s">
         <v>153</v>
@@ -3172,7 +3172,7 @@
         <v>141</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G84" t="s">
         <v>151</v>
@@ -3218,7 +3218,7 @@
         <v>143</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G86" t="s">
         <v>155</v>
@@ -3244,7 +3244,7 @@
         <v>156</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
@@ -3287,10 +3287,10 @@
         <v>87</v>
       </c>
       <c r="F89" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G89" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
@@ -3336,10 +3336,10 @@
         <v>92</v>
       </c>
       <c r="F91" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G91" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
@@ -3359,10 +3359,10 @@
         <v>91</v>
       </c>
       <c r="F92" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G92" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
@@ -3391,7 +3391,7 @@
   </sheetData>
   <autoFilter ref="A1:H80" xr:uid="{70EE433E-A0C3-6145-99B1-0D26F5A6E713}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H93">
-      <sortCondition ref="A1:A93"/>
+      <sortCondition ref="G1:G93"/>
     </sortState>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H93">
@@ -3415,7 +3415,7 @@
         <v>33</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -3430,7 +3430,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>171</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -3468,7 +3468,7 @@
         <v>167</v>
       </c>
       <c r="B11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -3508,7 +3508,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -3518,15 +3518,15 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -3561,7 +3561,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/data/actions/action_database_other_cbas.xlsx
+++ b/data/actions/action_database_other_cbas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/cc_offshore_wind/osw_mitigation_measures/data/actions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Library/CloudStorage/Dropbox/Chris/UCSB/projects/cc_offshore_wind/osw_mitigation_measures/data/actions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B65795-7C82-A645-8012-5244E1A62852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B9D47A-F418-8A40-8657-799121D48601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="500" windowWidth="33280" windowHeight="21900" xr2:uid="{D2A3E31B-314F-BE48-832E-3F962C44E348}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{D2A3E31B-314F-BE48-832E-3F962C44E348}"/>
   </bookViews>
   <sheets>
     <sheet name="Actions" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="285">
   <si>
     <t>source</t>
   </si>
@@ -896,6 +896,9 @@
   </si>
   <si>
     <t>CA-Santa Ynez Chumash-CADEMO.pdf</t>
+  </si>
+  <si>
+    <t>Avangrid</t>
   </si>
 </sst>
 </file>
@@ -1379,7 +1382,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="C2" t="s">
         <v>275</v>
@@ -1405,7 +1408,7 @@
         <v>70</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="C3" t="s">
         <v>275</v>
@@ -1434,7 +1437,7 @@
         <v>70</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="C4" t="s">
         <v>275</v>
@@ -1460,7 +1463,7 @@
         <v>70</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="C5" t="s">
         <v>275</v>
@@ -1486,7 +1489,7 @@
         <v>70</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="C6" t="s">
         <v>275</v>
